--- a/DataTables/DetailText/剧情/014_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/014_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DE9F4F-9BA4-4CA1-90EA-64B7DAF948E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC599302-882E-40E4-BB37-2B7461BF6E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="51">
   <si>
     <t>LineIndex</t>
   </si>
@@ -378,6 +367,13 @@
   </si>
   <si>
     <t>014治疗成功</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t>收入一两白银</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -389,7 +385,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -403,7 +399,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -424,7 +420,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -605,7 +601,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -884,25 +880,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1328125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.1328125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="22" customFormat="1">
       <c r="A1" s="15" t="s">
         <v>28</v>
       </c>
@@ -964,7 +960,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="22" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="22" customFormat="1">
       <c r="A2" s="11" t="s">
         <v>23</v>
       </c>
@@ -990,7 +986,9 @@
       <c r="M2" s="23"/>
       <c r="N2" s="24"/>
       <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
+      <c r="P2" s="24">
+        <v>1000</v>
+      </c>
       <c r="Q2" s="24"/>
       <c r="R2" s="25"/>
       <c r="S2" s="25" t="b">
@@ -1087,14 +1085,14 @@
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1319,14 +1317,20 @@
       <c r="I10" s="3"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="7"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="14" t="s">
+        <v>50</v>
+      </c>
       <c r="I11" s="3"/>
     </row>
     <row r="12" spans="1:9">
